--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484067_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484067_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7714</v>
+        <v>5.2079</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3945</v>
+        <v>4.4763</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3769</v>
+        <v>0.7316</v>
       </c>
       <c r="G2" t="n">
         <v>3.1437</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>3.084</v>
+        <v>1.5205</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7346</v>
+        <v>0.8163</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3494</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.9405</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4353</v>
+        <v>3.315</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3998</v>
+        <v>1.8306</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0355</v>
+        <v>1.4844</v>
       </c>
       <c r="G3" t="n">
         <v>2.6396</v>
@@ -688,13 +688,13 @@
         <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1801</v>
+        <v>-0.3004</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6631</v>
+        <v>-0.2323</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.517</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2065</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9321</v>
+        <v>1.6158</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7392</v>
+        <v>0.5351</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1929</v>
+        <v>1.0807</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7705</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9171</v>
+        <v>0.6008</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6746</v>
+        <v>0.4705</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2425</v>
+        <v>0.1303</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3036</v>
+        <v>1.3379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.081</v>
+        <v>0.1433</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2226</v>
+        <v>1.1946</v>
       </c>
       <c r="G5" t="n">
         <v>0.132</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0187</v>
+        <v>0.0156</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0396</v>
+        <v>0.0227</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0209</v>
+        <v>-0.0071</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6421</v>
+        <v>0.9136</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0905</v>
+        <v>1.167</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7326</v>
+        <v>-0.2533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2464</v>
+        <v>-1.3083</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5949</v>
+        <v>-0.983</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3485</v>
+        <v>-0.3252</v>
       </c>
       <c r="J6" t="n">
-        <v>0.958</v>
+        <v>0.6738</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9179</v>
+        <v>-0.4584</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>1.1322</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7116</v>
+        <v>-1.982</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.323</v>
+        <v>-0.5246</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3886</v>
+        <v>-1.4574</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3876</v>
+        <v>0.6348</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9353</v>
+        <v>0.4932</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4522</v>
+        <v>0.1416</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3367</v>
+        <v>0.7317</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0405</v>
+        <v>0.2673</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2961</v>
+        <v>0.4645</v>
       </c>
       <c r="G7" t="n">
         <v>2.2641</v>
@@ -1000,13 +1000,13 @@
         <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.721</v>
+        <v>-0.3259</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.289</v>
+        <v>-0.0623</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4319</v>
+        <v>-0.2636</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0046</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2487</v>
+        <v>-0.6403</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2533</v>
+        <v>0.6203</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3083</v>
+        <v>0.2464</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.983</v>
+        <v>0.5949</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3252</v>
+        <v>-0.3485</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6738</v>
+        <v>0.958</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4584</v>
+        <v>0.9179</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1322</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.982</v>
+        <v>-0.7116</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5246</v>
+        <v>-0.323</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4574</v>
+        <v>-0.3886</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5871</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2834</v>
+        <v>0.7255</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4251</v>
+        <v>0.3855</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1416</v>
+        <v>0.34</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8207</v>
+        <v>-2.9891</v>
       </c>
       <c r="E9" t="n">
         <v>-3.8751</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0543</v>
+        <v>0.886</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5659</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>0.721</v>
+        <v>0.5526</v>
       </c>
       <c r="T9" t="n">
         <v>0.3005</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4204</v>
+        <v>0.2521</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1583</v>
+        <v>-3.0234</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8293</v>
+        <v>-4.8066</v>
       </c>
       <c r="F10" t="n">
-        <v>1.671</v>
+        <v>1.7832</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7967</v>
@@ -1234,13 +1234,13 @@
         <v>3.1741</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6303</v>
+        <v>0.7652</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6463</v>
+        <v>0.669</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.016</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7724</v>
+        <v>-4.8009</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.9266</v>
+        <v>-6.2917</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1542</v>
+        <v>1.4908</v>
       </c>
       <c r="G11" t="n">
         <v>-3.673</v>
@@ -1312,13 +1312,13 @@
         <v>2.3806</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5124</v>
+        <v>0.4591</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4647</v>
+        <v>0.1701</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0476</v>
+        <v>0.289</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6652</v>
+        <v>2.288499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.8178</v>
+        <v>-7.194100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>9.482799999999999</v>
+        <v>9.482800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>1.311400000000001</v>
@@ -1360,10 +1360,10 @@
         <v>2.6718</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.360300000000001</v>
+        <v>-1.3603</v>
       </c>
       <c r="J12" t="n">
-        <v>7.657899999999999</v>
+        <v>7.657900000000001</v>
       </c>
       <c r="K12" t="n">
         <v>4.517099999999999</v>
@@ -1372,7 +1372,7 @@
         <v>3.141000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.3465</v>
+        <v>-6.346500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-1.8453</v>
@@ -1381,7 +1381,7 @@
         <v>-4.501300000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9920000000000007</v>
+        <v>-0.9920000000000002</v>
       </c>
       <c r="Q12" t="n">
         <v>-20.8303</v>
@@ -1390,10 +1390,10 @@
         <v>19.8383</v>
       </c>
       <c r="S12" t="n">
-        <v>4.0244</v>
+        <v>4.6478</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4098</v>
+        <v>3.0332</v>
       </c>
       <c r="U12" t="n">
         <v>1.6145</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.342</v>
+        <v>4.222</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1755</v>
+        <v>3.7876</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1665</v>
+        <v>0.4343</v>
       </c>
       <c r="G13" t="n">
         <v>3.0955</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1422</v>
+        <v>-0.2622</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6858</v>
+        <v>-0.0736</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4564</v>
+        <v>-0.1885</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8193</v>
+        <v>2.387</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5767</v>
+        <v>1.9892</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2426</v>
+        <v>0.3977</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3136</v>
+        <v>0.387</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5531</v>
+        <v>-1.7286</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7605</v>
+        <v>2.1156</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8155</v>
+        <v>2.3527</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7352</v>
+        <v>-0.6696</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0803</v>
+        <v>3.0223</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4981</v>
+        <v>-1.9658</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1821</v>
+        <v>-1.059</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6802</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1741</v>
+        <v>-1.1903</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.704</v>
+        <v>-0.5952</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9353</v>
+        <v>-0.3797</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2313</v>
+        <v>-0.2155</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2065</v>
+        <v>1.2065</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1387</v>
+        <v>2.3193</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9892</v>
+        <v>0.9645</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1495</v>
+        <v>1.3548</v>
       </c>
       <c r="G15" t="n">
-        <v>0.387</v>
+        <v>4.3136</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7286</v>
+        <v>3.5531</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1156</v>
+        <v>0.7605</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3527</v>
+        <v>3.8155</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6696</v>
+        <v>3.7352</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0223</v>
+        <v>0.0803</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9658</v>
+        <v>0.4981</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.059</v>
+        <v>-0.1821</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9068000000000001</v>
+        <v>0.6802</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="R15" t="n">
-        <v>2.579</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8434</v>
+        <v>0.2041</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3797</v>
+        <v>0.3231</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4637</v>
+        <v>-0.1191</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2065</v>
+        <v>-1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4472</v>
+        <v>0.6548</v>
       </c>
       <c r="E16" t="n">
-        <v>1.555</v>
+        <v>0.7388</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1078</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.1742</v>
@@ -1702,13 +1702,13 @@
         <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7924</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1168</v>
+        <v>0.3005</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3243</v>
+        <v>-0.3005</v>
       </c>
       <c r="V16" t="n">
         <v>0.8692</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0291</v>
+        <v>0.3054</v>
       </c>
       <c r="E17" t="n">
         <v>-1.0596</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0887</v>
+        <v>1.3651</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4839</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3146</v>
+        <v>0.5909</v>
       </c>
       <c r="T17" t="n">
         <v>0.5669</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2523</v>
+        <v>0.0241</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5998</v>
+        <v>-0.0226</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8186</v>
+        <v>-0.965</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2188</v>
+        <v>0.9425</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1918</v>
+        <v>-0.5555</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4287</v>
+        <v>0.1609</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7631</v>
+        <v>-0.7164</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2194</v>
+        <v>-0.0683</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5794</v>
+        <v>0.4085</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.64</v>
+        <v>-0.4768</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0277</v>
+        <v>-0.4872</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1507</v>
+        <v>-0.2477</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.123</v>
+        <v>-0.2396</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>0.179</v>
+        <v>-1.1379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8025</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2065</v>
+        <v>1.4724</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>1.4724</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.61</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8491</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2391</v>
+        <v>0.2952</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6588000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.348</v>
+        <v>-0.2919</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0425</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. ASSALIT GARCÍA</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0229</v>
+        <v>-0.6286</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4026</v>
+        <v>-2.6146</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3797</v>
+        <v>1.9859</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9232</v>
+        <v>-1.1918</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5747</v>
+        <v>-0.4287</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3485</v>
+        <v>-0.7631</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2771</v>
+        <v>-1.2194</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3173</v>
+        <v>-0.5794</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>-0.64</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.646</v>
+        <v>0.0277</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2574</v>
+        <v>0.1507</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3886</v>
+        <v>-0.123</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4954</v>
+        <v>0.1502</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0567</v>
+        <v>-0.4194</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4387</v>
+        <v>0.5696</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>X. ASSALIT GARCÍA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2715</v>
+        <v>-1.3511</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5772</v>
+        <v>-2.8107</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3057</v>
+        <v>1.4596</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5555</v>
+        <v>-0.9232</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1609</v>
+        <v>-0.5747</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7164</v>
+        <v>-0.3485</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0683</v>
+        <v>-0.2771</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4085</v>
+        <v>-0.3173</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4768</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4872</v>
+        <v>-0.646</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2477</v>
+        <v>-0.2574</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2396</v>
+        <v>-0.3886</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3868</v>
+        <v>0.1672</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.3514</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3893</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7599</v>
+        <v>-1.4598</v>
       </c>
       <c r="E22" t="n">
         <v>-1.4855</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2743</v>
+        <v>0.0258</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0474</v>
@@ -2170,13 +2170,13 @@
         <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5141</v>
+        <v>-0.214</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4988</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0153</v>
+        <v>0.2848</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9823</v>
+        <v>-2.6082</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1089</v>
+        <v>-3.0068</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1265</v>
+        <v>0.3986</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6313</v>
@@ -2248,13 +2248,13 @@
         <v>2.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.077</v>
+        <v>-0.7029</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2436</v>
+        <v>-0.1416</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8333</v>
+        <v>-0.5613</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8692</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1949</v>
+        <v>-2.8888</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4776</v>
+        <v>-4.1715</v>
       </c>
       <c r="F24" t="n">
         <v>1.2827</v>
@@ -2326,10 +2326,10 @@
         <v>1.9838</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1984</v>
+        <v>0.1077</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6121</v>
+        <v>-0.306</v>
       </c>
       <c r="U24" t="n">
         <v>0.4137</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.664999999999998</v>
+        <v>0.3754999999999988</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.482700000000001</v>
+        <v>-9.482699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>7.8177</v>
+        <v>9.8582</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3116</v>
@@ -2374,7 +2374,7 @@
         <v>-2.672</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3605</v>
+        <v>1.360500000000001</v>
       </c>
       <c r="J25" t="n">
         <v>6.346400000000001</v>
@@ -2383,7 +2383,7 @@
         <v>1.8451</v>
       </c>
       <c r="L25" t="n">
-        <v>4.501499999999999</v>
+        <v>4.501499999999998</v>
       </c>
       <c r="M25" t="n">
         <v>-7.658</v>
@@ -2395,7 +2395,7 @@
         <v>-3.141100000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9920000000000001</v>
+        <v>0.9919999999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-19.8382</v>
@@ -2404,13 +2404,13 @@
         <v>20.8303</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.024500000000001</v>
+        <v>-1.984</v>
       </c>
       <c r="T25" t="n">
         <v>-1.6147</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.4096</v>
+        <v>-0.3690999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>2.6789</v>
